--- a/data/trans_dic/P7_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P7_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 20,2</t>
+          <t>14,3; 19,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,27; 21,26</t>
+          <t>15,31; 21,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 19,72</t>
+          <t>14,09; 19,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,92; 26,54</t>
+          <t>19,63; 26,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,78; 33,74</t>
+          <t>26,64; 33,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,45; 31,24</t>
+          <t>24,31; 31,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,7; 30,52</t>
+          <t>23,8; 30,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,36; 28,7</t>
+          <t>20,72; 28,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,31; 25,81</t>
+          <t>21,35; 25,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,18</t>
+          <t>20,78; 25,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 24,31</t>
+          <t>19,7; 24,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,32; 26,74</t>
+          <t>21,36; 26,68</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 17,82</t>
+          <t>13,46; 17,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 20,16</t>
+          <t>15,14; 20,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 18,16</t>
+          <t>13,33; 17,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,51</t>
+          <t>5,53; 15,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,64; 34,89</t>
+          <t>28,82; 34,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,43; 30,22</t>
+          <t>24,62; 30,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,34; 27,12</t>
+          <t>21,51; 26,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,4; 26,77</t>
+          <t>22,32; 26,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,82; 25,86</t>
+          <t>21,71; 25,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,56; 24,62</t>
+          <t>20,52; 24,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 21,76</t>
+          <t>18,12; 21,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 20,16</t>
+          <t>11,34; 20,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 19,15</t>
+          <t>13,01; 18,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 19,63</t>
+          <t>13,78; 19,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,4; 18,51</t>
+          <t>13,2; 18,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,91</t>
+          <t>13,16; 19,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,23; 29,86</t>
+          <t>23,21; 29,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,26; 31,2</t>
+          <t>24,12; 30,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,08; 25,36</t>
+          <t>18,98; 25,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 21,54</t>
+          <t>7,33; 21,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,0; 23,4</t>
+          <t>19,06; 23,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,06; 24,32</t>
+          <t>20,03; 24,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,94; 21,21</t>
+          <t>16,97; 21,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,53; 18,62</t>
+          <t>10,73; 18,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,34; 16,49</t>
+          <t>12,45; 16,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,72; 17,6</t>
+          <t>12,63; 17,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,85; 17,7</t>
+          <t>12,63; 17,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,47; 21,59</t>
+          <t>16,48; 21,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 29,45</t>
+          <t>23,76; 29,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,15; 27,49</t>
+          <t>21,95; 27,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,3; 25,94</t>
+          <t>20,39; 25,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,2; 25,52</t>
+          <t>18,57; 25,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 22,58</t>
+          <t>18,78; 22,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,21; 21,83</t>
+          <t>18,19; 21,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,43; 21,24</t>
+          <t>17,4; 21,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 22,87</t>
+          <t>18,55; 22,76</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,44; 16,89</t>
+          <t>14,38; 16,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 18,12</t>
+          <t>15,41; 18,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,37; 16,95</t>
+          <t>14,47; 17,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,81; 18,25</t>
+          <t>12,65; 18,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,94; 30,19</t>
+          <t>27,03; 30,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,08; 28,21</t>
+          <t>25,05; 28,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,34; 25,42</t>
+          <t>22,44; 25,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 24,02</t>
+          <t>17,86; 24,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,21; 23,28</t>
+          <t>21,29; 23,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,7; 22,78</t>
+          <t>20,88; 22,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,94; 20,91</t>
+          <t>18,93; 20,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,03; 20,9</t>
+          <t>16,65; 20,79</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con salud general regular o mala</t>
+          <t>Población con salud general regular o mala (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>99731; 140190</t>
+          <t>99270; 137694</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107319; 149403</t>
+          <t>107590; 148905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93460; 133049</t>
+          <t>95063; 132407</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126609; 168649</t>
+          <t>124737; 165428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>184366; 232220</t>
+          <t>183371; 229766</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>170447; 217731</t>
+          <t>169450; 217603</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>159474; 205342</t>
+          <t>160108; 204660</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>147676; 208147</t>
+          <t>150276; 208675</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>294624; 356839</t>
+          <t>295141; 358232</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>286348; 352501</t>
+          <t>290904; 358452</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>267068; 327575</t>
+          <t>265546; 324178</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>290134; 363827</t>
+          <t>290593; 362993</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126645; 171152</t>
+          <t>129277; 172112</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>154860; 204813</t>
+          <t>153790; 206500</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>137068; 185470</t>
+          <t>136136; 183637</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76341; 184973</t>
+          <t>65991; 183417</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>277368; 337858</t>
+          <t>279053; 337292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>251466; 311051</t>
+          <t>253455; 313830</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>221911; 281971</t>
+          <t>223632; 279886</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>214599; 256531</t>
+          <t>213874; 257647</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>421017; 498802</t>
+          <t>418829; 494234</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>420578; 503479</t>
+          <t>419633; 499535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>374074; 448526</t>
+          <t>373529; 446965</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>243777; 433561</t>
+          <t>243970; 434384</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90890; 129963</t>
+          <t>88293; 127913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>101518; 148059</t>
+          <t>103950; 145878</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101751; 140575</t>
+          <t>100286; 141882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91302; 133273</t>
+          <t>92724; 134811</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>158870; 204221</t>
+          <t>158722; 203136</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>188563; 242456</t>
+          <t>187443; 240745</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>149556; 198785</t>
+          <t>148771; 197149</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>78288; 201036</t>
+          <t>68450; 200239</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>258847; 318757</t>
+          <t>259683; 318422</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>307261; 372491</t>
+          <t>306755; 373447</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>261400; 327332</t>
+          <t>261921; 325177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>172441; 304981</t>
+          <t>175828; 307090</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>116263; 155354</t>
+          <t>117297; 159007</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>120395; 166590</t>
+          <t>119568; 164750</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119980; 165279</t>
+          <t>117965; 162492</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>152625; 200101</t>
+          <t>152765; 197776</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>246583; 305877</t>
+          <t>246792; 302472</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>232535; 288642</t>
+          <t>230442; 288976</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>211685; 270542</t>
+          <t>212636; 270269</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>199305; 279380</t>
+          <t>203308; 281403</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>375996; 447191</t>
+          <t>372051; 447400</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>363640; 435924</t>
+          <t>363233; 437727</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>344468; 419880</t>
+          <t>343979; 418089</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>374194; 462436</t>
+          <t>375079; 460242</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>473016; 553293</t>
+          <t>471042; 554950</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>524226; 619743</t>
+          <t>527114; 618993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>486983; 574639</t>
+          <t>490583; 576108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>443052; 631334</t>
+          <t>437516; 633711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>910198; 1020177</t>
+          <t>913456; 1021116</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>891178; 1002317</t>
+          <t>890066; 1002703</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>790681; 899567</t>
+          <t>794259; 899176</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>662368; 891380</t>
+          <t>662805; 891266</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1411771; 1549058</t>
+          <t>1417103; 1550198</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1443221; 1588498</t>
+          <t>1455838; 1589881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1312133; 1448582</t>
+          <t>1311433; 1441627</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1221613; 1499044</t>
+          <t>1193805; 1491182</t>
         </is>
       </c>
     </row>
